--- a/src/ExcelsiorClosedXml.Tests/EnumerableStringTests.WithNewlines.verified.xlsx
+++ b/src/ExcelsiorClosedXml.Tests/EnumerableStringTests.WithNewlines.verified.xlsx
@@ -47,8 +47,16 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="1">
+  <x:fonts count="2">
     <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
@@ -83,13 +91,20 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -400,18 +415,18 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" ht="14.25" customHeight="1">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2" ht="199.5" customHeight="1">
-      <x:c r="A2" s="1" t="s">
+      <x:c r="A2" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="2" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/src/ExcelsiorClosedXml.Tests/EnumerableStringTests.WithNewlines.verified.xlsx
+++ b/src/ExcelsiorClosedXml.Tests/EnumerableStringTests.WithNewlines.verified.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$2</x:definedName>
-  </x:definedNames>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId4"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$2</definedName>
+  </definedNames>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Value1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Value2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>● a
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>Value1</t>
+  </si>
+  <si>
+    <t>Value2</t>
+  </si>
+  <si>
+    <t>● a
 ● a
 ● a
 ● a
@@ -37,86 +37,86 @@
 a
 ● a
 ● a
-● a</x:t>
-  </x:si>
-</x:sst>
+● a</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="0" formatCode=""/>
-  </x:numFmts>
-  <x:fonts count="2">
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="2">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="none">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="none">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="none">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-  </x:cellStyleXfs>
-  <x:cellXfs count="3">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="0" formatCode=""/>
+  </numFmts>
+  <fonts count="2">
+    <font>
+      <vertAlign val="baseline"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="baseline"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border diagonalUp="0" diagonalDown="0">
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal style="none">
+        <color rgb="FF000000"/>
+      </diagonal>
+    </border>
+  </borders>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <protection locked="1" hidden="0"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -403,39 +403,39 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:B2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="9.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.710625" style="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:2" ht="14.25" customHeight="1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:2" ht="199.5" customHeight="1">
-      <x:c r="A2" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:autoFilter ref="A1:B2"/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.710625" style="0" customWidth="1"/>
+    <col min="2" max="2" width="14.710625" style="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="199.5" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B2"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
--- a/src/ExcelsiorClosedXml.Tests/EnumerableStringTests.WithNewlines.verified.xlsx
+++ b/src/ExcelsiorClosedXml.Tests/EnumerableStringTests.WithNewlines.verified.xlsx
@@ -24,20 +24,350 @@
     <t>Value2</t>
   </si>
   <si>
-    <t>● a
-● a
-● a
-● a
-● a
-● a
-a
-● a
-a
-● a
-a
-● a
-● a
-● a</t>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">a
+a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">a
+a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">a
+a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -422,7 +752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="199.5" customHeight="1">
+    <row r="2" spans="1:2" ht="185.25" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>

--- a/src/ExcelsiorClosedXml.Tests/EnumerableStringTests.WithNewlines.verified.xlsx
+++ b/src/ExcelsiorClosedXml.Tests/EnumerableStringTests.WithNewlines.verified.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="DeterministicId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -761,7 +761,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B2"/>
+  <autoFilter ref="A1:A2"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
